--- a/Task 3 excel (version 2).xlsx
+++ b/Task 3 excel (version 2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library2\Desktop\Harshi DA18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC23\Desktop\Harshi DA-18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10020001_{E0122E6B-E17A-470A-B192-C9D58972BD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D978EA4-1C1A-48AD-ACEE-919D20C4905B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="5" xr2:uid="{A5788E9E-6B29-4F0C-869F-0E5DEF9171AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{A5788E9E-6B29-4F0C-869F-0E5DEF9171AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <sheet name="Sheet10" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -722,7 +721,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -880,7 +879,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1003,9 +1001,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1043,7 +1041,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1149,7 +1147,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1291,7 +1289,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1475,10 +1473,10 @@
       <c r="A1" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>113</v>
       </c>
       <c r="D1" s="48" t="s">
@@ -1489,10 +1487,10 @@
       <c r="A2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="59">
+      <c r="B2" s="58">
         <v>2</v>
       </c>
-      <c r="C2" s="59">
+      <c r="C2" s="58">
         <v>85</v>
       </c>
       <c r="D2" s="49" t="s">
@@ -1503,10 +1501,10 @@
       <c r="A3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="59">
         <v>0</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="59">
         <v>78</v>
       </c>
       <c r="D3" s="51" t="s">
@@ -1517,10 +1515,10 @@
       <c r="A4" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <v>4</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4" s="58">
         <v>91</v>
       </c>
       <c r="D4" s="49" t="s">
@@ -1531,10 +1529,10 @@
       <c r="A5" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="59">
         <v>1</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="59">
         <v>68</v>
       </c>
       <c r="D5" s="51" t="s">
@@ -1847,7 +1845,7 @@
     <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1883,8 +1881,11 @@
       <c r="D2" s="50">
         <v>46211</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="E2" s="55" t="str">
+        <f>IF(D2-C2&gt;7,"Late Rerurned","Returned on time")</f>
+        <v>Returned on time</v>
+      </c>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
@@ -1899,7 +1900,10 @@
       <c r="D3" s="52">
         <v>46221</v>
       </c>
-      <c r="E3" s="55"/>
+      <c r="E3" s="55" t="str">
+        <f t="shared" ref="E3:E4" si="0">IF(D3-C3&gt;7,"Late Rerurned","Returned on time")</f>
+        <v>Late Rerurned</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49" t="s">
@@ -1914,7 +1918,10 @@
       <c r="D4" s="50">
         <v>46215</v>
       </c>
-      <c r="E4" s="55"/>
+      <c r="E4" s="55" t="str">
+        <f t="shared" si="0"/>
+        <v>Returned on time</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1936,10 +1943,10 @@
       <c r="C1" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="57" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1953,10 +1960,10 @@
       <c r="C2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="59">
+      <c r="D2" s="58">
         <v>2</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="58">
         <v>350</v>
       </c>
     </row>
@@ -1970,10 +1977,10 @@
       <c r="C3" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="59">
         <v>3</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="59">
         <v>180</v>
       </c>
     </row>
@@ -1987,10 +1994,10 @@
       <c r="C4" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="58">
         <v>1</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="58">
         <v>280</v>
       </c>
     </row>
@@ -2004,10 +2011,10 @@
       <c r="C5" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="59">
         <v>4</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="59">
         <v>350</v>
       </c>
     </row>
@@ -2079,10 +2086,10 @@
       <c r="A1" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2090,10 +2097,10 @@
       <c r="A2" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="59">
+      <c r="B2" s="58">
         <v>450</v>
       </c>
-      <c r="C2" s="59">
+      <c r="C2" s="58">
         <v>8</v>
       </c>
     </row>
@@ -2101,10 +2108,10 @@
       <c r="A3" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="59">
         <v>320</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="59">
         <v>7</v>
       </c>
     </row>
@@ -2112,10 +2119,10 @@
       <c r="A4" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <v>520</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4" s="58">
         <v>9</v>
       </c>
     </row>
@@ -2123,10 +2130,10 @@
       <c r="A5" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="59">
         <v>280</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="59">
         <v>6</v>
       </c>
     </row>
@@ -2144,13 +2151,13 @@
       <c r="A1" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="57" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="57" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2158,13 +2165,13 @@
       <c r="A2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="59">
+      <c r="B2" s="58">
         <v>22</v>
       </c>
       <c r="C2" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="59">
+      <c r="D2" s="58">
         <v>2500</v>
       </c>
     </row>
@@ -2172,13 +2179,13 @@
       <c r="A3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="59">
         <v>45</v>
       </c>
       <c r="C3" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="59">
         <v>1800</v>
       </c>
     </row>
@@ -2186,13 +2193,13 @@
       <c r="A4" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <v>31</v>
       </c>
       <c r="C4" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="58">
         <v>4000</v>
       </c>
     </row>
@@ -2200,13 +2207,13 @@
       <c r="A5" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="59">
         <v>26</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="59">
         <v>2500</v>
       </c>
     </row>
@@ -2227,7 +2234,7 @@
       <c r="B1" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>99</v>
       </c>
       <c r="D1" s="48" t="s">
@@ -2241,7 +2248,7 @@
       <c r="B2" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="59">
+      <c r="C2" s="58">
         <v>5000</v>
       </c>
       <c r="D2" s="49" t="s">
@@ -2255,7 +2262,7 @@
       <c r="B3" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="59">
         <v>6000</v>
       </c>
       <c r="D3" s="51" t="s">
@@ -2269,7 +2276,7 @@
       <c r="B4" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4" s="58">
         <v>7000</v>
       </c>
       <c r="D4" s="49" t="s">
@@ -2283,7 +2290,7 @@
       <c r="B5" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="59">
         <v>8000</v>
       </c>
       <c r="D5" s="51" t="s">
